--- a/data/violation_groundtruth.xlsx
+++ b/data/violation_groundtruth.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sahyasree.mp\Desktop\CCT_AGENT\misra_checker\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sahyasree.mp\Desktop\CCT_AGENT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>File Name</t>
   </si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>Assembly language shall be encapsulated and isolated. Bare 'asm("NOP")' calls appear inline without encapsulation in a macro (e.g. #define NOP asm("NOP")) or dedicated assembler/C function.</t>
-  </si>
-  <si>
-    <t>Second inline 'asm("NOP")' on the same line — same Rule 2.1 violation: assembly instructions must be isolated, not scattered inline in production function bodies.</t>
   </si>
   <si>
     <t>data.c</t>
@@ -433,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -475,7 +472,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>8</v>
@@ -499,59 +496,45 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="3">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="C6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="2">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="B7" s="2">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="3">
-        <v>4</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="2">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
